--- a/Version_Info.xlsx
+++ b/Version_Info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Obras\Documents\GitHub\Sistema-Financeiro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F10A5D9-6151-4CE4-8081-0C7D6E9996F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B3E74E9-37CA-4AA5-8655-C7AE545D7F1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13485" yWindow="825" windowWidth="12330" windowHeight="14910" xr2:uid="{30F240C2-A098-48F6-BD2E-0F632F0648BA}"/>
+    <workbookView xWindow="13290" yWindow="90" windowWidth="15285" windowHeight="14910" xr2:uid="{30F240C2-A098-48F6-BD2E-0F632F0648BA}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>major</t>
   </si>
@@ -134,12 +134,21 @@
   <si>
     <t>"Modificados todos relatórios para identificar o 'STATUS' dos lançamentos",</t>
   </si>
+  <si>
+    <t>"Instalado sistema de Backup Automático contra quedas/travamentos"</t>
+  </si>
+  <si>
+    <t>"Melhoria no relatório de Tipos de Despesas, mostrando o total geral por tipo e gráfico de linha do tempo"</t>
+  </si>
+  <si>
+    <t>"Melhoria no relatório de Categoria, mostrando o total geral por categoria e gráfico de linha do tempo"</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -175,6 +184,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -196,7 +213,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -221,6 +238,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -536,7 +556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8ECF308-2BDA-44B4-A992-93448DFE394D}">
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="9.140625" style="2"/>
@@ -735,6 +755,36 @@
         <v>27</v>
       </c>
     </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="2">
+        <v>1</v>
+      </c>
+      <c r="B27" s="2">
+        <v>3</v>
+      </c>
+      <c r="C27" s="2">
+        <v>1</v>
+      </c>
+      <c r="D27" s="3">
+        <v>45812</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E28" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E29" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="9"/>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>

--- a/Version_Info.xlsx
+++ b/Version_Info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Obras\Documents\GitHub\Sistema-Financeiro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B3E74E9-37CA-4AA5-8655-C7AE545D7F1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E798BB9-B88D-48C7-99E2-BD92783F755B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="13290" yWindow="90" windowWidth="15285" windowHeight="14910" xr2:uid="{30F240C2-A098-48F6-BD2E-0F632F0648BA}"/>
   </bookViews>

--- a/Version_Info.xlsx
+++ b/Version_Info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Obras\Documents\GitHub\Sistema-Financeiro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E798BB9-B88D-48C7-99E2-BD92783F755B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D60879EF-08EB-4952-960E-558F1074755B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="13290" yWindow="90" windowWidth="15285" windowHeight="14910" xr2:uid="{30F240C2-A098-48F6-BD2E-0F632F0648BA}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>major</t>
   </si>
@@ -142,6 +142,12 @@
   </si>
   <si>
     <t>"Melhoria no relatório de Categoria, mostrando o total geral por categoria e gráfico de linha do tempo"</t>
+  </si>
+  <si>
+    <t>"Inclusão de Visualizador de Lançamentos de Fornecedor"</t>
+  </si>
+  <si>
+    <t>"Inclusão de Correção Monetária para contratos de administração, dependendo de teste para ser totalmente implementada."</t>
   </si>
 </sst>
 </file>
@@ -556,7 +562,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8ECF308-2BDA-44B4-A992-93448DFE394D}">
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="9.140625" style="2"/>
@@ -783,7 +789,26 @@
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="9"/>
+      <c r="A30" s="9">
+        <v>1</v>
+      </c>
+      <c r="B30" s="2">
+        <v>3</v>
+      </c>
+      <c r="C30" s="2">
+        <v>2</v>
+      </c>
+      <c r="D30" s="3">
+        <v>45821</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E31" s="1" t="s">
+        <v>34</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/Version_Info.xlsx
+++ b/Version_Info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Obras\Documents\GitHub\Sistema-Financeiro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D60879EF-08EB-4952-960E-558F1074755B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86757A62-637E-433D-B4C6-CCFC7FCA5971}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13290" yWindow="90" windowWidth="15285" windowHeight="14910" xr2:uid="{30F240C2-A098-48F6-BD2E-0F632F0648BA}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="15090" windowHeight="14910" xr2:uid="{30F240C2-A098-48F6-BD2E-0F632F0648BA}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>major</t>
   </si>
@@ -148,6 +148,12 @@
   </si>
   <si>
     <t>"Inclusão de Correção Monetária para contratos de administração, dependendo de teste para ser totalmente implementada."</t>
+  </si>
+  <si>
+    <t>"Adicão de funcionalidade para cadastro de fornecedor PF sem CPF"</t>
+  </si>
+  <si>
+    <t>"Melhoria no Relatório de Fornecedores com a inclusão de opção para mostrar quais clientes adquiriram itens de um dado fornecedor "</t>
   </si>
 </sst>
 </file>
@@ -562,7 +568,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8ECF308-2BDA-44B4-A992-93448DFE394D}">
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="9.140625" style="2"/>
@@ -799,14 +805,26 @@
         <v>2</v>
       </c>
       <c r="D30" s="3">
-        <v>45821</v>
+        <v>45824</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="9"/>
       <c r="E31" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A32" s="9"/>
+      <c r="E32" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="33" spans="5:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E33" s="1" t="s">
         <v>34</v>
       </c>
     </row>

--- a/Version_Info.xlsx
+++ b/Version_Info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Obras\Documents\GitHub\Sistema-Financeiro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86757A62-637E-433D-B4C6-CCFC7FCA5971}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C45B3FC-1FFD-456E-97C7-DA9F21F9BCA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="15090" windowHeight="14910" xr2:uid="{30F240C2-A098-48F6-BD2E-0F632F0648BA}"/>
+    <workbookView xWindow="13755" yWindow="1320" windowWidth="14775" windowHeight="12960" xr2:uid="{30F240C2-A098-48F6-BD2E-0F632F0648BA}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t>major</t>
   </si>
@@ -154,6 +154,18 @@
   </si>
   <si>
     <t>"Melhoria no Relatório de Fornecedores com a inclusão de opção para mostrar quais clientes adquiriram itens de um dado fornecedor "</t>
+  </si>
+  <si>
+    <t>"Alteração do Relatório de Despesas para incluir o PDF Temporário"</t>
+  </si>
+  <si>
+    <t>"Exclusão do ordenamento dos pagamentos de Diaristas para ser pela entrada e não por valor pago"</t>
+  </si>
+  <si>
+    <t>"Exclusão do ordenamento dos pagamentos das despesas pagas pelo Cliente para ser pela entrada e não por data de vencimento"</t>
+  </si>
+  <si>
+    <t>"Inclusão de Importação de planilha com dados de TRANSPORTE e CAFÉ"</t>
   </si>
 </sst>
 </file>
@@ -225,7 +237,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -253,6 +265,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -568,7 +583,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8ECF308-2BDA-44B4-A992-93448DFE394D}">
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="9.140625" style="2"/>
@@ -823,9 +838,41 @@
         <v>36</v>
       </c>
     </row>
-    <row r="33" spans="5:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="E33" s="1" t="s">
         <v>34</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
+        <v>1</v>
+      </c>
+      <c r="B34" s="2">
+        <v>3</v>
+      </c>
+      <c r="C34" s="2">
+        <v>3</v>
+      </c>
+      <c r="D34" s="3">
+        <v>45847</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E35" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E36" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E37" s="1" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/Version_Info.xlsx
+++ b/Version_Info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Obras\Documents\GitHub\Sistema-Financeiro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C45B3FC-1FFD-456E-97C7-DA9F21F9BCA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D21C516C-6626-406E-8A3A-77530352E443}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13755" yWindow="1320" windowWidth="14775" windowHeight="12960" xr2:uid="{30F240C2-A098-48F6-BD2E-0F632F0648BA}"/>
+    <workbookView xWindow="15450" yWindow="360" windowWidth="13170" windowHeight="14130" xr2:uid="{30F240C2-A098-48F6-BD2E-0F632F0648BA}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <si>
     <t>major</t>
   </si>
@@ -166,6 +166,12 @@
   </si>
   <si>
     <t>"Inclusão de Importação de planilha com dados de TRANSPORTE e CAFÉ"</t>
+  </si>
+  <si>
+    <t>"Adição de funcionalidade para recálculo de taxa de administração por percentual, sempre que houver inclusão, alteração ou exclusão de lançamento"</t>
+  </si>
+  <si>
+    <t>"Melhoria na funcionalidade que detecta duplicidade de lançamento"</t>
   </si>
 </sst>
 </file>
@@ -237,7 +243,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -265,9 +271,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -583,7 +586,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8ECF308-2BDA-44B4-A992-93448DFE394D}">
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="9.140625" style="2"/>
@@ -861,7 +864,7 @@
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E35" s="10" t="s">
+      <c r="E35" s="1" t="s">
         <v>37</v>
       </c>
     </row>
@@ -873,6 +876,28 @@
     <row r="37" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="E37" s="1" t="s">
         <v>39</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A38" s="2">
+        <v>1</v>
+      </c>
+      <c r="B38" s="2">
+        <v>3</v>
+      </c>
+      <c r="C38" s="2">
+        <v>4</v>
+      </c>
+      <c r="D38" s="3">
+        <v>45860</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E39" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/Version_Info.xlsx
+++ b/Version_Info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Obras\Documents\GitHub\Sistema-Financeiro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D21C516C-6626-406E-8A3A-77530352E443}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D21311A8-2354-4317-A365-3EEC35B16AB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15450" yWindow="360" windowWidth="13170" windowHeight="14130" xr2:uid="{30F240C2-A098-48F6-BD2E-0F632F0648BA}"/>
+    <workbookView xWindow="13515" yWindow="390" windowWidth="10545" windowHeight="14130" xr2:uid="{30F240C2-A098-48F6-BD2E-0F632F0648BA}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
   <si>
     <t>major</t>
   </si>
@@ -172,6 +172,18 @@
   </si>
   <si>
     <t>"Melhoria na funcionalidade que detecta duplicidade de lançamento"</t>
+  </si>
+  <si>
+    <t>"Correção do cálculo de taxa de administração, considerando apenas lançamentos do tipo 'ATIVO'."</t>
+  </si>
+  <si>
+    <t>"Inclusão do campo 'NF' no Gerenciador de Lançamentos"</t>
+  </si>
+  <si>
+    <t>"Inclusão de botões de 'EXCLUSÃO/RESTAURAÇÃO' de várias despesas no Gerenciador de Lançamentos."</t>
+  </si>
+  <si>
+    <t>"Inclusão do campo 'ETAPA DA OBRA' na Entrada de Dados, com manutenção através das Configurações do Sistema."</t>
   </si>
 </sst>
 </file>
@@ -586,7 +598,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8ECF308-2BDA-44B4-A992-93448DFE394D}">
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="9.140625" style="2"/>
@@ -883,21 +895,41 @@
         <v>1</v>
       </c>
       <c r="B38" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C38" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D38" s="3">
-        <v>45860</v>
+        <v>45881</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="E39" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E40" s="1" t="s">
         <v>42</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E41" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E42" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E43" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/Version_Info.xlsx
+++ b/Version_Info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Obras\Documents\GitHub\Sistema-Financeiro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D21311A8-2354-4317-A365-3EEC35B16AB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EAF7A1C-6C7D-4013-9E45-A0D20EE0DD36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13515" yWindow="390" windowWidth="10545" windowHeight="14130" xr2:uid="{30F240C2-A098-48F6-BD2E-0F632F0648BA}"/>
+    <workbookView xWindow="825" yWindow="285" windowWidth="14820" windowHeight="14130" xr2:uid="{30F240C2-A098-48F6-BD2E-0F632F0648BA}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
   <si>
     <t>major</t>
   </si>
@@ -185,12 +185,32 @@
   <si>
     <t>"Inclusão do campo 'ETAPA DA OBRA' na Entrada de Dados, com manutenção através das Configurações do Sistema."</t>
   </si>
+  <si>
+    <r>
+      <t>"Inclusão de gerenciamento para excluir CPF temporário"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF292929"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <t>"Inclusão de funcionalidade para importaçãoo de NFe via XML e Chave de Acesso, permitindo salvar dados financeiros e materiais na planilha do cliente"</t>
+  </si>
+  <si>
+    <t>"Inclusão de campo 'INSUMO' na Entrada de Dados, com manutenção através das Configurações do Sistema",</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -234,6 +254,11 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -255,7 +280,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -283,6 +308,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -598,7 +626,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8ECF308-2BDA-44B4-A992-93448DFE394D}">
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="9.140625" style="2"/>
@@ -898,10 +926,10 @@
         <v>4</v>
       </c>
       <c r="C38" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D38" s="3">
-        <v>45881</v>
+        <v>45891</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>41</v>
@@ -930,6 +958,21 @@
     <row r="43" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="E43" s="1" t="s">
         <v>46</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E44" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E45" s="10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E46" s="1" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/Version_Info.xlsx
+++ b/Version_Info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Obras\Documents\GitHub\Sistema-Financeiro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EAF7A1C-6C7D-4013-9E45-A0D20EE0DD36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC1D26E5-05DE-4B1B-85A6-8167B0F9A56E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="825" yWindow="285" windowWidth="14820" windowHeight="14130" xr2:uid="{30F240C2-A098-48F6-BD2E-0F632F0648BA}"/>
+    <workbookView xWindow="9495" yWindow="60" windowWidth="14820" windowHeight="14130" xr2:uid="{30F240C2-A098-48F6-BD2E-0F632F0648BA}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
   <si>
     <t>major</t>
   </si>
@@ -204,6 +204,12 @@
   </si>
   <si>
     <t>"Inclusão de campo 'INSUMO' na Entrada de Dados, com manutenção através das Configurações do Sistema",</t>
+  </si>
+  <si>
+    <t>"Melhoria no Visualizador de Lançamentos de Fornecedor que agora possui todas as funcionalidades do Gerenciador de Lançamentos"</t>
+  </si>
+  <si>
+    <t>"Correção na aba Entrada de Dados que não estava limpando corretamente todos os campos"</t>
   </si>
 </sst>
 </file>
@@ -626,7 +632,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8ECF308-2BDA-44B4-A992-93448DFE394D}">
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="9.140625" style="2"/>
@@ -975,6 +981,28 @@
         <v>48</v>
       </c>
     </row>
+    <row r="47" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A47" s="2">
+        <v>1</v>
+      </c>
+      <c r="B47" s="2">
+        <v>4</v>
+      </c>
+      <c r="C47" s="2">
+        <v>1</v>
+      </c>
+      <c r="D47" s="3">
+        <v>45897</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E48" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>

--- a/Version_Info.xlsx
+++ b/Version_Info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Obras\Documents\GitHub\Sistema-Financeiro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC1D26E5-05DE-4B1B-85A6-8167B0F9A56E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DBA3A61-2DE5-43C8-91AC-B588453E2770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9495" yWindow="60" windowWidth="14820" windowHeight="14130" xr2:uid="{30F240C2-A098-48F6-BD2E-0F632F0648BA}"/>
+    <workbookView xWindow="13770" yWindow="195" windowWidth="14820" windowHeight="14130" xr2:uid="{30F240C2-A098-48F6-BD2E-0F632F0648BA}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
   <si>
     <t>major</t>
   </si>
@@ -210,6 +210,15 @@
   </si>
   <si>
     <t>"Correção na aba Entrada de Dados que não estava limpando corretamente todos os campos"</t>
+  </si>
+  <si>
+    <t>"Correção do Backup Automático para verificar o Cliente antes de salvar"</t>
+  </si>
+  <si>
+    <t>"Inclusão de autocompletar nos campos 'Etapa da Obra' e 'Insumo' na aba Entrada de Dados"</t>
+  </si>
+  <si>
+    <t>"Correção de EXCLUIR/RESTAURAR individual no Gerenciador de Lançamentos"</t>
   </si>
 </sst>
 </file>
@@ -632,7 +641,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8ECF308-2BDA-44B4-A992-93448DFE394D}">
-  <dimension ref="A1:E48"/>
+  <dimension ref="A1:E51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="9.140625" style="2"/>
@@ -1003,6 +1012,33 @@
         <v>51</v>
       </c>
     </row>
+    <row r="49" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A49" s="2">
+        <v>1</v>
+      </c>
+      <c r="B49" s="2">
+        <v>4</v>
+      </c>
+      <c r="C49" s="2">
+        <v>2</v>
+      </c>
+      <c r="D49" s="3">
+        <v>45905</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E50" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E51" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>

--- a/Version_Info.xlsx
+++ b/Version_Info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Obras\Documents\GitHub\Sistema-Financeiro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DBA3A61-2DE5-43C8-91AC-B588453E2770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8FFB352-1DF9-456F-8BF8-90A1B1023C2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13770" yWindow="195" windowWidth="14820" windowHeight="14130" xr2:uid="{30F240C2-A098-48F6-BD2E-0F632F0648BA}"/>
+    <workbookView xWindow="13650" yWindow="615" windowWidth="14820" windowHeight="14130" xr2:uid="{30F240C2-A098-48F6-BD2E-0F632F0648BA}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
   <si>
     <t>major</t>
   </si>
@@ -219,6 +219,15 @@
   </si>
   <si>
     <t>"Correção de EXCLUIR/RESTAURAR individual no Gerenciador de Lançamentos"</t>
+  </si>
+  <si>
+    <t>"Inclusão da opção Dinheiro em Dados Bancários na entrada de dados"</t>
+  </si>
+  <si>
+    <t>Melhorias no parcelamento, permitindo a entrada de parcelas com diferentes valores"</t>
+  </si>
+  <si>
+    <t>"Inclusão de Agenda com dados pré-definidos e lançamentos futuros"</t>
   </si>
 </sst>
 </file>
@@ -641,7 +650,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8ECF308-2BDA-44B4-A992-93448DFE394D}">
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="9.140625" style="2"/>
@@ -1039,6 +1048,33 @@
         <v>52</v>
       </c>
     </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="2">
+        <v>1</v>
+      </c>
+      <c r="B52" s="2">
+        <v>4</v>
+      </c>
+      <c r="C52" s="2">
+        <v>3</v>
+      </c>
+      <c r="D52" s="3">
+        <v>45924</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E53" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E54" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>

--- a/Version_Info.xlsx
+++ b/Version_Info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Obras\Documents\GitHub\Sistema-Financeiro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8FFB352-1DF9-456F-8BF8-90A1B1023C2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E82A791-2DEF-405C-B6B9-22AE8EF6C7D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13650" yWindow="615" windowWidth="14820" windowHeight="14130" xr2:uid="{30F240C2-A098-48F6-BD2E-0F632F0648BA}"/>
+    <workbookView xWindow="13920" yWindow="0" windowWidth="14820" windowHeight="14130" xr2:uid="{30F240C2-A098-48F6-BD2E-0F632F0648BA}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
   <si>
     <t>major</t>
   </si>
@@ -228,6 +228,9 @@
   </si>
   <si>
     <t>"Inclusão de Agenda com dados pré-definidos e lançamentos futuros"</t>
+  </si>
+  <si>
+    <t>"Correção do filtro de datas do Gerenciador de Lançamentos, que estava trazendo a data do dia se outras funcionalidades eram chamadas."</t>
   </si>
 </sst>
 </file>
@@ -284,12 +287,18 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -304,7 +313,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -335,6 +344,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -650,7 +662,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8ECF308-2BDA-44B4-A992-93448DFE394D}">
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="9.140625" style="2"/>
@@ -1075,6 +1087,21 @@
         <v>57</v>
       </c>
     </row>
+    <row r="55" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A55" s="2">
+        <v>1</v>
+      </c>
+      <c r="B55" s="2">
+        <v>4</v>
+      </c>
+      <c r="C55" s="2">
+        <v>4</v>
+      </c>
+      <c r="D55" s="11"/>
+      <c r="E55" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>

--- a/Version_Info.xlsx
+++ b/Version_Info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Obras\Documents\GitHub\Sistema-Financeiro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E82A791-2DEF-405C-B6B9-22AE8EF6C7D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BA9742F-C2C1-4C31-917D-9DF14AAD0C49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13920" yWindow="0" windowWidth="14820" windowHeight="14130" xr2:uid="{30F240C2-A098-48F6-BD2E-0F632F0648BA}"/>
+    <workbookView xWindow="6600" yWindow="0" windowWidth="22140" windowHeight="14130" xr2:uid="{30F240C2-A098-48F6-BD2E-0F632F0648BA}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
   <si>
     <t>major</t>
   </si>
@@ -230,7 +230,16 @@
     <t>"Inclusão de Agenda com dados pré-definidos e lançamentos futuros"</t>
   </si>
   <si>
-    <t>"Correção do filtro de datas do Gerenciador de Lançamentos, que estava trazendo a data do dia se outras funcionalidades eram chamadas."</t>
+    <t>"Correção do filtro de datas do Gerenciador de Lançamentos, que estava trazendo a data do dia se, outras funcionalidades fossem chamadas."</t>
+  </si>
+  <si>
+    <t>"Inclusão de edição de Taxa de Administração do tipo Fixo"</t>
+  </si>
+  <si>
+    <t>"Melhoria no Visualizador de Lançamentos de Pendentes, que elimina registros duplicados ao salvar na planilha"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Correção da compensação de Taxa de Administração caso fossem detectados valores errados em períodos anteriores" </t>
   </si>
 </sst>
 </file>
@@ -287,18 +296,12 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -313,7 +316,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -344,9 +347,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -662,7 +662,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8ECF308-2BDA-44B4-A992-93448DFE394D}">
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:E58"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="9.140625" style="2"/>
@@ -1097,9 +1097,26 @@
       <c r="C55" s="2">
         <v>4</v>
       </c>
-      <c r="D55" s="11"/>
+      <c r="D55" s="3">
+        <v>45947</v>
+      </c>
       <c r="E55" s="1" t="s">
         <v>58</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E56" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E57" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E58" s="1" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/Version_Info.xlsx
+++ b/Version_Info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Obras\Documents\GitHub\Sistema-Financeiro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BA9742F-C2C1-4C31-917D-9DF14AAD0C49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8141A6B-3023-4F44-BB9E-D511BDD24756}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6600" yWindow="0" windowWidth="22140" windowHeight="14130" xr2:uid="{30F240C2-A098-48F6-BD2E-0F632F0648BA}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
   <si>
     <t>major</t>
   </si>
@@ -240,6 +240,12 @@
   </si>
   <si>
     <t xml:space="preserve">"Correção da compensação de Taxa de Administração caso fossem detectados valores errados em períodos anteriores" </t>
+  </si>
+  <si>
+    <t>"Correção na importação de dados de RH após mudança de versão do Excel na origem do arquivo"</t>
+  </si>
+  <si>
+    <t>"Disponibilizada a importação da planilha de RH oriúnda do sistema Domínio"</t>
   </si>
 </sst>
 </file>
@@ -662,7 +668,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8ECF308-2BDA-44B4-A992-93448DFE394D}">
-  <dimension ref="A1:E58"/>
+  <dimension ref="A1:E60"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="9.140625" style="2"/>
@@ -798,325 +804,335 @@
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="2">
-        <v>1</v>
-      </c>
-      <c r="B19" s="2">
+      <c r="E19" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
+        <v>1</v>
+      </c>
+      <c r="B20" s="2">
         <v>2</v>
       </c>
-      <c r="C19" s="2">
-        <v>1</v>
-      </c>
-      <c r="D19" s="3">
+      <c r="C20" s="2">
+        <v>1</v>
+      </c>
+      <c r="D20" s="3">
         <v>45797</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="E20" s="1" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E20" s="1" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E21" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E22" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E23" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A23" s="2">
-        <v>1</v>
-      </c>
-      <c r="B23" s="2">
+    <row r="24" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
+        <v>1</v>
+      </c>
+      <c r="B24" s="2">
         <v>3</v>
       </c>
-      <c r="C23" s="2">
+      <c r="C24" s="2">
         <v>0</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D24" s="3">
         <v>45806</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="E24" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="E24" s="8" t="s">
+    <row r="25" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E25" s="8" t="s">
         <v>28</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E25" s="8" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E26" s="8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E27" s="8" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="2">
-        <v>1</v>
-      </c>
-      <c r="B27" s="2">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
+        <v>1</v>
+      </c>
+      <c r="B28" s="2">
         <v>3</v>
       </c>
-      <c r="C27" s="2">
-        <v>1</v>
-      </c>
-      <c r="D27" s="3">
+      <c r="C28" s="2">
+        <v>1</v>
+      </c>
+      <c r="D28" s="3">
         <v>45812</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="E28" s="1" t="s">
         <v>30</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="E28" s="1" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="E29" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E30" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="9">
-        <v>1</v>
-      </c>
-      <c r="B30" s="2">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="9">
+        <v>1</v>
+      </c>
+      <c r="B31" s="2">
         <v>3</v>
       </c>
-      <c r="C30" s="2">
+      <c r="C31" s="2">
         <v>2</v>
       </c>
-      <c r="D30" s="3">
+      <c r="D31" s="3">
         <v>45824</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="E31" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="9"/>
-      <c r="E31" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="9"/>
       <c r="E32" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A33" s="9"/>
+      <c r="E33" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="E33" s="1" t="s">
+    <row r="34" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E34" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="2">
-        <v>1</v>
-      </c>
-      <c r="B34" s="2">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="2">
+        <v>1</v>
+      </c>
+      <c r="B35" s="2">
         <v>3</v>
       </c>
-      <c r="C34" s="2">
+      <c r="C35" s="2">
         <v>3</v>
       </c>
-      <c r="D34" s="3">
+      <c r="D35" s="3">
         <v>45847</v>
       </c>
-      <c r="E34" s="1" t="s">
+      <c r="E35" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E35" s="1" t="s">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E36" s="1" t="s">
         <v>37</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="E36" s="1" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="E37" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E38" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A38" s="2">
-        <v>1</v>
-      </c>
-      <c r="B38" s="2">
+    <row r="39" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A39" s="2">
+        <v>1</v>
+      </c>
+      <c r="B39" s="2">
         <v>4</v>
       </c>
-      <c r="C38" s="2">
+      <c r="C39" s="2">
         <v>0</v>
       </c>
-      <c r="D38" s="3">
+      <c r="D39" s="3">
         <v>45891</v>
       </c>
-      <c r="E38" s="1" t="s">
+      <c r="E39" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="E39" s="1" t="s">
+    <row r="40" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E40" s="1" t="s">
         <v>43</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E40" s="1" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E41" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E42" s="1" t="s">
         <v>44</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="E42" s="1" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="E43" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E44" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E44" s="1" t="s">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E45" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="E45" s="10" t="s">
+    <row r="46" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E46" s="10" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="E46" s="1" t="s">
+    <row r="47" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E47" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A47" s="2">
-        <v>1</v>
-      </c>
-      <c r="B47" s="2">
+    <row r="48" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A48" s="2">
+        <v>1</v>
+      </c>
+      <c r="B48" s="2">
         <v>4</v>
       </c>
-      <c r="C47" s="2">
-        <v>1</v>
-      </c>
-      <c r="D47" s="3">
+      <c r="C48" s="2">
+        <v>1</v>
+      </c>
+      <c r="D48" s="3">
         <v>45897</v>
       </c>
-      <c r="E47" s="1" t="s">
+      <c r="E48" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="E48" s="1" t="s">
+    <row r="49" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E49" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A49" s="2">
-        <v>1</v>
-      </c>
-      <c r="B49" s="2">
+    <row r="50" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A50" s="2">
+        <v>1</v>
+      </c>
+      <c r="B50" s="2">
         <v>4</v>
       </c>
-      <c r="C49" s="2">
+      <c r="C50" s="2">
         <v>2</v>
       </c>
-      <c r="D49" s="3">
+      <c r="D50" s="3">
         <v>45905</v>
       </c>
-      <c r="E49" s="1" t="s">
+      <c r="E50" s="1" t="s">
         <v>53</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E50" s="1" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E51" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E52" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="2">
-        <v>1</v>
-      </c>
-      <c r="B52" s="2">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="2">
+        <v>1</v>
+      </c>
+      <c r="B53" s="2">
         <v>4</v>
       </c>
-      <c r="C52" s="2">
+      <c r="C53" s="2">
         <v>3</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D53" s="3">
         <v>45924</v>
       </c>
-      <c r="E52" s="1" t="s">
+      <c r="E53" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="E53" s="1" t="s">
+    <row r="54" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E54" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E54" s="1" t="s">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E55" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A55" s="2">
-        <v>1</v>
-      </c>
-      <c r="B55" s="2">
+    <row r="56" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A56" s="2">
+        <v>1</v>
+      </c>
+      <c r="B56" s="2">
         <v>4</v>
       </c>
-      <c r="C55" s="2">
+      <c r="C56" s="2">
         <v>4</v>
       </c>
-      <c r="D55" s="3">
+      <c r="D56" s="3">
         <v>45947</v>
       </c>
-      <c r="E55" s="1" t="s">
+      <c r="E56" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="E56" s="1" t="s">
+    <row r="57" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E57" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E57" s="1" t="s">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E58" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="E58" s="1" t="s">
+    <row r="59" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E59" s="1" t="s">
         <v>60</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E60" s="1" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/Version_Info.xlsx
+++ b/Version_Info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Obras\Documents\GitHub\Sistema-Financeiro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8141A6B-3023-4F44-BB9E-D511BDD24756}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E15E5A57-2544-4B96-88F9-177375B1275E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6600" yWindow="0" windowWidth="22140" windowHeight="14130" xr2:uid="{30F240C2-A098-48F6-BD2E-0F632F0648BA}"/>
+    <workbookView xWindow="13740" yWindow="90" windowWidth="14925" windowHeight="15420" xr2:uid="{30F240C2-A098-48F6-BD2E-0F632F0648BA}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
   <si>
     <t>major</t>
   </si>
@@ -246,6 +246,26 @@
   </si>
   <si>
     <t>"Disponibilizada a importação da planilha de RH oriúnda do sistema Domínio"</t>
+  </si>
+  <si>
+    <r>
+      <t>"Inclusão de campo para Notas no final do relatório"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF292929"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <t>"Correção para inclusão de lançamentos futuros no relatório"</t>
+  </si>
+  <si>
+    <t>XX/11/2025</t>
   </si>
 </sst>
 </file>
@@ -322,7 +342,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -353,6 +373,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -668,7 +691,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8ECF308-2BDA-44B4-A992-93448DFE394D}">
-  <dimension ref="A1:E60"/>
+  <dimension ref="A1:E62"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="9.140625" style="2"/>
@@ -1135,6 +1158,29 @@
         <v>62</v>
       </c>
     </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="2">
+        <v>1</v>
+      </c>
+      <c r="B61" s="2">
+        <v>4</v>
+      </c>
+      <c r="C61" s="2">
+        <v>5</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D62" s="11"/>
+      <c r="E62" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>

--- a/Version_Info.xlsx
+++ b/Version_Info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Obras\Documents\GitHub\Sistema-Financeiro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E15E5A57-2544-4B96-88F9-177375B1275E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A71FF9B-12A0-4554-8B1C-48FE31C37631}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13740" yWindow="90" windowWidth="14925" windowHeight="15420" xr2:uid="{30F240C2-A098-48F6-BD2E-0F632F0648BA}"/>
+    <workbookView xWindow="-360" yWindow="1005" windowWidth="14925" windowHeight="14385" xr2:uid="{30F240C2-A098-48F6-BD2E-0F632F0648BA}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
   <si>
     <t>major</t>
   </si>
@@ -200,9 +200,6 @@
     </r>
   </si>
   <si>
-    <t>"Inclusão de funcionalidade para importaçãoo de NFe via XML e Chave de Acesso, permitindo salvar dados financeiros e materiais na planilha do cliente"</t>
-  </si>
-  <si>
     <t>"Inclusão de campo 'INSUMO' na Entrada de Dados, com manutenção através das Configurações do Sistema",</t>
   </si>
   <si>
@@ -265,7 +262,13 @@
     <t>"Correção para inclusão de lançamentos futuros no relatório"</t>
   </si>
   <si>
-    <t>XX/11/2025</t>
+    <t>"Inclusão de vinculação de medições de contratos à despesa lançada",</t>
+  </si>
+  <si>
+    <t>"Adição de diferenciação visual entre ambientes TESTE e PRODUÇÃO"</t>
+  </si>
+  <si>
+    <t>"Inclusão de funcionalidade para importação de NFe via XML e Chave de Acesso, permitindo salvar dados financeiros e materiais na planilha do cliente"</t>
   </si>
 </sst>
 </file>
@@ -691,7 +694,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8ECF308-2BDA-44B4-A992-93448DFE394D}">
-  <dimension ref="A1:E62"/>
+  <dimension ref="A1:E64"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="9.140625" style="2"/>
@@ -828,7 +831,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E19" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -1037,12 +1040,12 @@
     </row>
     <row r="46" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="E46" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="E47" s="1" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="30" x14ac:dyDescent="0.25">
@@ -1059,12 +1062,12 @@
         <v>45897</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="E49" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="30" x14ac:dyDescent="0.25">
@@ -1081,17 +1084,17 @@
         <v>45905</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E51" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E52" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
@@ -1108,17 +1111,17 @@
         <v>45924</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="E54" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E55" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="30" x14ac:dyDescent="0.25">
@@ -1135,27 +1138,27 @@
         <v>45947</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="E57" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E58" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="E59" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="E60" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -1168,17 +1171,27 @@
       <c r="C61" s="2">
         <v>5</v>
       </c>
-      <c r="D61" s="3" t="s">
-        <v>66</v>
+      <c r="D61" s="3">
+        <v>45957</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D62" s="11"/>
       <c r="E62" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E63" s="1" t="s">
         <v>65</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E64" s="1" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/Version_Info.xlsx
+++ b/Version_Info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Obras\Documents\GitHub\Sistema-Financeiro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A71FF9B-12A0-4554-8B1C-48FE31C37631}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B87E1CD1-F11A-4D94-97CD-93AB60D81A6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-360" yWindow="1005" windowWidth="14925" windowHeight="14385" xr2:uid="{30F240C2-A098-48F6-BD2E-0F632F0648BA}"/>
+    <workbookView xWindow="13845" yWindow="885" windowWidth="14925" windowHeight="14385" xr2:uid="{30F240C2-A098-48F6-BD2E-0F632F0648BA}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="76">
   <si>
     <t>major</t>
   </si>
@@ -270,12 +270,54 @@
   <si>
     <t>"Inclusão de funcionalidade para importação de NFe via XML e Chave de Acesso, permitindo salvar dados financeiros e materiais na planilha do cliente"</t>
   </si>
+  <si>
+    <r>
+      <t>"Inclusão de Etapa da Obra nas importações de dados de RH - Folha e Transporte &amp; Café"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF292929"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <t>"Inclusão da opção de remover vários regitros de uma vez só no Visualizador de Lançamentos",</t>
+  </si>
+  <si>
+    <t>"Inclusão da opção de vincular parcelas do contrato de administração de obra a lançamentos efetuados",</t>
+  </si>
+  <si>
+    <t>"Relatório de Despesas Aprimorado: adição de numeração de páginas",</t>
+  </si>
+  <si>
+    <t>"Relatório de Despesas Aprimorado: mudança de Notas para a primeira página e arquivada na planilha do cliente",</t>
+  </si>
+  <si>
+    <t>"Relatório de Despesas Aprimorado: adição de data de vencimento para 13º, Férias e Rescisão",</t>
+  </si>
+  <si>
+    <t>"Mudança do botão 'Visualizar Lançamentos' para a seção de Gerenciamento de Dados"</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"Correção dos dados bancários na Agenda",</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -323,6 +365,11 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -694,7 +741,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8ECF308-2BDA-44B4-A992-93448DFE394D}">
-  <dimension ref="A1:E64"/>
+  <dimension ref="A1:E72"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="9.140625" style="2"/>
@@ -1194,6 +1241,58 @@
         <v>66</v>
       </c>
     </row>
+    <row r="65" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A65" s="2">
+        <v>1</v>
+      </c>
+      <c r="B65" s="2">
+        <v>5</v>
+      </c>
+      <c r="C65" s="2">
+        <v>0</v>
+      </c>
+      <c r="D65" s="3">
+        <v>45976</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E66" s="8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E67" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E68" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E69" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E70" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E71" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E72" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>

--- a/Version_Info.xlsx
+++ b/Version_Info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Obras\Documents\GitHub\Sistema-Financeiro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B87E1CD1-F11A-4D94-97CD-93AB60D81A6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A376D64B-2771-4D33-AB71-21A7EEE9CF13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13845" yWindow="885" windowWidth="14925" windowHeight="14385" xr2:uid="{30F240C2-A098-48F6-BD2E-0F632F0648BA}"/>
+    <workbookView xWindow="13590" yWindow="1740" windowWidth="13005" windowHeight="12795" xr2:uid="{30F240C2-A098-48F6-BD2E-0F632F0648BA}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="79">
   <si>
     <t>major</t>
   </si>
@@ -311,6 +311,15 @@
       </rPr>
       <t>"Correção dos dados bancários na Agenda",</t>
     </r>
+  </si>
+  <si>
+    <t>Incluída a opção de editar em massa no visualizador.</t>
+  </si>
+  <si>
+    <t>Inclusão de aba Serviços para ser utilizado nos contratos de prestação de serviço</t>
+  </si>
+  <si>
+    <t>Criação de módulo para geração de contrato de prestação de serviço</t>
   </si>
 </sst>
 </file>
@@ -741,7 +750,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8ECF308-2BDA-44B4-A992-93448DFE394D}">
-  <dimension ref="A1:E72"/>
+  <dimension ref="A1:E75"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="9.140625" style="2"/>
@@ -1293,6 +1302,30 @@
         <v>74</v>
       </c>
     </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="2">
+        <v>1</v>
+      </c>
+      <c r="B73" s="2">
+        <v>5</v>
+      </c>
+      <c r="C73" s="2">
+        <v>1</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E74" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E75" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>

--- a/Version_Info.xlsx
+++ b/Version_Info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Obras\Documents\GitHub\Sistema-Financeiro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A376D64B-2771-4D33-AB71-21A7EEE9CF13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BC7FB0A-328D-4526-8BC3-EC18200E29C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="13590" yWindow="1740" windowWidth="13005" windowHeight="12795" xr2:uid="{30F240C2-A098-48F6-BD2E-0F632F0648BA}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="81">
   <si>
     <t>major</t>
   </si>
@@ -320,6 +320,12 @@
   </si>
   <si>
     <t>Criação de módulo para geração de contrato de prestação de serviço</t>
+  </si>
+  <si>
+    <t>Inclusão de campos para CPF, CNO, rstado civil e grupo em Clientes.xlsx, para emissão de contrato de prestação de serviço</t>
+  </si>
+  <si>
+    <t>Inclusão de campo endereço em base_fornecedores.xlsx, para emissão de contrato de prestação de serviço</t>
   </si>
 </sst>
 </file>
@@ -750,7 +756,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8ECF308-2BDA-44B4-A992-93448DFE394D}">
-  <dimension ref="A1:E75"/>
+  <dimension ref="A1:E77"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="9.140625" style="2"/>
@@ -1326,6 +1332,16 @@
         <v>78</v>
       </c>
     </row>
+    <row r="76" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E76" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E77" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>

--- a/Version_Info.xlsx
+++ b/Version_Info.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Obras\Documents\GitHub\Sistema-Financeiro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BC7FB0A-328D-4526-8BC3-EC18200E29C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C605E1A4-7024-41C6-BEEE-6CD67A3023CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13590" yWindow="1740" windowWidth="13005" windowHeight="12795" xr2:uid="{30F240C2-A098-48F6-BD2E-0F632F0648BA}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="13005" windowHeight="12795" xr2:uid="{30F240C2-A098-48F6-BD2E-0F632F0648BA}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>

--- a/Version_Info.xlsx
+++ b/Version_Info.xlsx
@@ -8,15 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Obras\Documents\GitHub\Sistema-Financeiro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C605E1A4-7024-41C6-BEEE-6CD67A3023CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB96BA7D-B201-48BA-B51C-479AE625DC7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="13005" windowHeight="12795" xr2:uid="{30F240C2-A098-48F6-BD2E-0F632F0648BA}"/>
+    <workbookView xWindow="0" yWindow="1200" windowWidth="14355" windowHeight="14400" xr2:uid="{30F240C2-A098-48F6-BD2E-0F632F0648BA}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -33,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="88">
   <si>
     <t>major</t>
   </si>
@@ -327,6 +326,27 @@
   </si>
   <si>
     <t>Inclusão de campo endereço em base_fornecedores.xlsx, para emissão de contrato de prestação de serviço</t>
+  </si>
+  <si>
+    <t>Incluída a opção de vincular várias medições a um único pagamento</t>
+  </si>
+  <si>
+    <t>Criação do relatório gerencial de contratos de empreiteiros</t>
+  </si>
+  <si>
+    <t>Incluído Data Fim nos contratos de empreiteiros</t>
+  </si>
+  <si>
+    <t>Alteração do texto "Complemento de Caixa" para "Despesas pagas pelo Caixa" no Relatório de Despesas</t>
+  </si>
+  <si>
+    <t>Incluída a opção de copiar as fases/eventos de um gestor para outro no contrato de administração de obra</t>
+  </si>
+  <si>
+    <t>Incluída a opção de vincular várias parcelas de contrato de administração de obra a um lançamento na planilha do cliente</t>
+  </si>
+  <si>
+    <t>Incluída a opção de contrato de medição apenas com prazo, sem data início e fim</t>
   </si>
 </sst>
 </file>
@@ -757,7 +777,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8ECF308-2BDA-44B4-A992-93448DFE394D}">
-  <dimension ref="A1:E77"/>
+  <dimension ref="A1:E84"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="9.140625" style="2"/>
@@ -1319,6 +1339,9 @@
       <c r="C73" s="2">
         <v>1</v>
       </c>
+      <c r="D73" s="3">
+        <v>45992</v>
+      </c>
       <c r="E73" s="2" t="s">
         <v>76</v>
       </c>
@@ -1341,6 +1364,53 @@
     <row r="77" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="E77" s="1" t="s">
         <v>80</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="2">
+        <v>1</v>
+      </c>
+      <c r="B78" s="2">
+        <v>5</v>
+      </c>
+      <c r="C78" s="2">
+        <v>2</v>
+      </c>
+      <c r="D78" s="3">
+        <v>46000</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E79" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E80" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="81" spans="5:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E81" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="82" spans="5:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E82" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="83" spans="5:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E83" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="84" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E84" s="1" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>

--- a/Version_Info.xlsx
+++ b/Version_Info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Obras\Documents\GitHub\Sistema-Financeiro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB96BA7D-B201-48BA-B51C-479AE625DC7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9E77C17-6C9E-4723-85F3-D094DEC5A963}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1200" windowWidth="14355" windowHeight="14400" xr2:uid="{30F240C2-A098-48F6-BD2E-0F632F0648BA}"/>
+    <workbookView xWindow="13965" yWindow="1170" windowWidth="14355" windowHeight="14400" xr2:uid="{30F240C2-A098-48F6-BD2E-0F632F0648BA}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>

--- a/Version_Info.xlsx
+++ b/Version_Info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Obras\Documents\GitHub\Sistema-Financeiro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9E77C17-6C9E-4723-85F3-D094DEC5A963}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD83CBAE-8036-4356-BCAA-A4593F4B3EB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13965" yWindow="1170" windowWidth="14355" windowHeight="14400" xr2:uid="{30F240C2-A098-48F6-BD2E-0F632F0648BA}"/>
+    <workbookView xWindow="3855" yWindow="1200" windowWidth="14355" windowHeight="14400" xr2:uid="{30F240C2-A098-48F6-BD2E-0F632F0648BA}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="89">
   <si>
     <t>major</t>
   </si>
@@ -347,6 +347,9 @@
   </si>
   <si>
     <t>Incluída a opção de contrato de medição apenas com prazo, sem data início e fim</t>
+  </si>
+  <si>
+    <t>Inclusão e gestão de medições pendentes na Agenda</t>
   </si>
 </sst>
 </file>
@@ -777,7 +780,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8ECF308-2BDA-44B4-A992-93448DFE394D}">
-  <dimension ref="A1:E84"/>
+  <dimension ref="A1:E85"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="9.140625" style="2"/>
@@ -1413,6 +1416,11 @@
         <v>87</v>
       </c>
     </row>
+    <row r="85" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E85" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>

--- a/Version_Info.xlsx
+++ b/Version_Info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Obras\Documents\GitHub\Sistema-Financeiro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD83CBAE-8036-4356-BCAA-A4593F4B3EB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51C0E38F-DA69-4E3C-B040-A1FCC265DD48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3855" yWindow="1200" windowWidth="14355" windowHeight="14400" xr2:uid="{30F240C2-A098-48F6-BD2E-0F632F0648BA}"/>
+    <workbookView xWindow="10305" yWindow="915" windowWidth="14835" windowHeight="14400" xr2:uid="{30F240C2-A098-48F6-BD2E-0F632F0648BA}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="90">
   <si>
     <t>major</t>
   </si>
@@ -350,6 +350,9 @@
   </si>
   <si>
     <t>Inclusão e gestão de medições pendentes na Agenda</t>
+  </si>
+  <si>
+    <t>Incluída a opção de importar medições originárias do Relatório de Medições</t>
   </si>
 </sst>
 </file>
@@ -780,7 +783,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8ECF308-2BDA-44B4-A992-93448DFE394D}">
-  <dimension ref="A1:E85"/>
+  <dimension ref="A1:E86"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="9.140625" style="2"/>
@@ -1380,7 +1383,7 @@
         <v>2</v>
       </c>
       <c r="D78" s="3">
-        <v>46000</v>
+        <v>46003</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>81</v>
@@ -1418,6 +1421,11 @@
     </row>
     <row r="85" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E85" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="86" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E86" s="1" t="s">
         <v>88</v>
       </c>
     </row>

--- a/Version_Info.xlsx
+++ b/Version_Info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Obras\Documents\GitHub\Sistema-Financeiro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51C0E38F-DA69-4E3C-B040-A1FCC265DD48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA324489-DB85-418F-9C76-377CA41EBDC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="10305" yWindow="915" windowWidth="14835" windowHeight="14400" xr2:uid="{30F240C2-A098-48F6-BD2E-0F632F0648BA}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="91">
   <si>
     <t>major</t>
   </si>
@@ -353,6 +353,9 @@
   </si>
   <si>
     <t>Incluída a opção de importar medições originárias do Relatório de Medições</t>
+  </si>
+  <si>
+    <t>Relatório Quinzenal de Medições - em PDF, para incluir na documentação do cliente</t>
   </si>
 </sst>
 </file>
@@ -783,7 +786,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8ECF308-2BDA-44B4-A992-93448DFE394D}">
-  <dimension ref="A1:E86"/>
+  <dimension ref="A1:E87"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="9.140625" style="2"/>
@@ -1383,7 +1386,7 @@
         <v>2</v>
       </c>
       <c r="D78" s="3">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>81</v>
@@ -1427,6 +1430,11 @@
     <row r="86" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E86" s="1" t="s">
         <v>88</v>
+      </c>
+    </row>
+    <row r="87" spans="5:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E87" s="1" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>

--- a/Version_Info.xlsx
+++ b/Version_Info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Obras\Documents\GitHub\Sistema-Financeiro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA324489-DB85-418F-9C76-377CA41EBDC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF6760B5-3379-4312-B250-4786934D06AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10305" yWindow="915" windowWidth="14835" windowHeight="14400" xr2:uid="{30F240C2-A098-48F6-BD2E-0F632F0648BA}"/>
+    <workbookView xWindow="13740" yWindow="660" windowWidth="14835" windowHeight="14400" xr2:uid="{30F240C2-A098-48F6-BD2E-0F632F0648BA}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="93">
   <si>
     <t>major</t>
   </si>
@@ -356,6 +356,12 @@
   </si>
   <si>
     <t>Relatório Quinzenal de Medições - em PDF, para incluir na documentação do cliente</t>
+  </si>
+  <si>
+    <t>Atualização do cadastro de Clientes para incluir metragem de alvará e separar campos do endereço</t>
+  </si>
+  <si>
+    <t>Correção de edição em massa no Gerenciador de Lançamentos</t>
   </si>
 </sst>
 </file>
@@ -786,7 +792,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8ECF308-2BDA-44B4-A992-93448DFE394D}">
-  <dimension ref="A1:E87"/>
+  <dimension ref="A1:E89"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="9.140625" style="2"/>
@@ -1386,7 +1392,7 @@
         <v>2</v>
       </c>
       <c r="D78" s="3">
-        <v>46006</v>
+        <v>46009</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>81</v>
@@ -1435,6 +1441,16 @@
     <row r="87" spans="5:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E87" s="1" t="s">
         <v>90</v>
+      </c>
+    </row>
+    <row r="88" spans="5:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E88" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="89" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E89" s="1" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>

--- a/Version_Info.xlsx
+++ b/Version_Info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Obras\Documents\GitHub\Sistema-Financeiro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF6760B5-3379-4312-B250-4786934D06AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC574059-8D33-43DB-A5CB-6CEFAEB305DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13740" yWindow="660" windowWidth="14835" windowHeight="14400" xr2:uid="{30F240C2-A098-48F6-BD2E-0F632F0648BA}"/>
+    <workbookView xWindow="15945" yWindow="540" windowWidth="10800" windowHeight="14400" xr2:uid="{30F240C2-A098-48F6-BD2E-0F632F0648BA}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="94">
   <si>
     <t>major</t>
   </si>
@@ -362,6 +362,9 @@
   </si>
   <si>
     <t>Correção de edição em massa no Gerenciador de Lançamentos</t>
+  </si>
+  <si>
+    <t>Inclusão de busca por múltiplos campos no Gerenciador de Lançamentos</t>
   </si>
 </sst>
 </file>
@@ -792,7 +795,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8ECF308-2BDA-44B4-A992-93448DFE394D}">
-  <dimension ref="A1:E89"/>
+  <dimension ref="A1:E90"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="9.140625" style="2"/>
@@ -1453,6 +1456,11 @@
         <v>92</v>
       </c>
     </row>
+    <row r="90" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E90" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>

--- a/Version_Info.xlsx
+++ b/Version_Info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Obras\Documents\GitHub\Sistema-Financeiro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC574059-8D33-43DB-A5CB-6CEFAEB305DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2972379-D9E3-42D6-84D6-E68EB9159BC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15945" yWindow="540" windowWidth="10800" windowHeight="14400" xr2:uid="{30F240C2-A098-48F6-BD2E-0F632F0648BA}"/>
+    <workbookView xWindow="3510" yWindow="1050" windowWidth="14685" windowHeight="15150" xr2:uid="{30F240C2-A098-48F6-BD2E-0F632F0648BA}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
   <si>
     <t>major</t>
   </si>
@@ -365,6 +365,9 @@
   </si>
   <si>
     <t>Inclusão de busca por múltiplos campos no Gerenciador de Lançamentos</t>
+  </si>
+  <si>
+    <t>Melhoria na sincronização do Visualizador de Lançamentos</t>
   </si>
 </sst>
 </file>
@@ -795,7 +798,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8ECF308-2BDA-44B4-A992-93448DFE394D}">
-  <dimension ref="A1:E90"/>
+  <dimension ref="A1:E91"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="9.140625" style="2"/>
@@ -1411,54 +1414,71 @@
         <v>83</v>
       </c>
     </row>
-    <row r="81" spans="5:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="E81" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="82" spans="5:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="E82" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="83" spans="5:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="E83" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="84" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E84" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="85" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E85" s="1" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="86" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E86" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="87" spans="5:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E87" s="1" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="88" spans="5:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="E88" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="89" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E89" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="90" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E90" s="1" t="s">
         <v>93</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" s="2">
+        <v>1</v>
+      </c>
+      <c r="B91" s="2">
+        <v>5</v>
+      </c>
+      <c r="C91" s="2">
+        <v>3</v>
+      </c>
+      <c r="D91" s="3">
+        <v>46024</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/Version_Info.xlsx
+++ b/Version_Info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Obras\Documents\GitHub\Sistema-Financeiro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2972379-D9E3-42D6-84D6-E68EB9159BC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5488EEB-CF55-421B-89A7-72F9BF4D1D29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="1050" windowWidth="14685" windowHeight="15150" xr2:uid="{30F240C2-A098-48F6-BD2E-0F632F0648BA}"/>
+    <workbookView xWindow="14115" yWindow="150" windowWidth="14685" windowHeight="15150" xr2:uid="{30F240C2-A098-48F6-BD2E-0F632F0648BA}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="96">
   <si>
     <t>major</t>
   </si>
@@ -368,6 +368,9 @@
   </si>
   <si>
     <t>Melhoria na sincronização do Visualizador de Lançamentos</t>
+  </si>
+  <si>
+    <t>Correção no travamento e saída do sistema</t>
   </si>
 </sst>
 </file>
@@ -798,7 +801,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8ECF308-2BDA-44B4-A992-93448DFE394D}">
-  <dimension ref="A1:E91"/>
+  <dimension ref="A1:E92"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="9.140625" style="2"/>
@@ -1481,6 +1484,11 @@
         <v>94</v>
       </c>
     </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E92" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>

--- a/Version_Info.xlsx
+++ b/Version_Info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Obras\Documents\GitHub\Sistema-Financeiro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5488EEB-CF55-421B-89A7-72F9BF4D1D29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0521490-76C2-4408-AD5E-4AE386BF4557}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14115" yWindow="150" windowWidth="14685" windowHeight="15150" xr2:uid="{30F240C2-A098-48F6-BD2E-0F632F0648BA}"/>
+    <workbookView xWindow="13710" yWindow="2565" windowWidth="14685" windowHeight="12690" xr2:uid="{30F240C2-A098-48F6-BD2E-0F632F0648BA}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="100">
   <si>
     <t>major</t>
   </si>
@@ -371,6 +371,18 @@
   </si>
   <si>
     <t>Correção no travamento e saída do sistema</t>
+  </si>
+  <si>
+    <t>Correção de edição em massa no Visualizador de Lançamentos</t>
+  </si>
+  <si>
+    <t>Correção no lançamento de medições</t>
+  </si>
+  <si>
+    <t>Correção na inclusão de contrato de administração com mais de um administrador</t>
+  </si>
+  <si>
+    <t>Outras correções menores e melhorias de desempenho</t>
   </si>
 </sst>
 </file>
@@ -801,7 +813,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8ECF308-2BDA-44B4-A992-93448DFE394D}">
-  <dimension ref="A1:E92"/>
+  <dimension ref="A1:E97"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="9.140625" style="2"/>
@@ -1478,7 +1490,7 @@
         <v>3</v>
       </c>
       <c r="D91" s="3">
-        <v>46024</v>
+        <v>46034</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>94</v>
@@ -1487,6 +1499,31 @@
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E92" s="1" t="s">
         <v>95</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E93" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E94" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E95" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E96" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="97" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E97" s="1" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/Version_Info.xlsx
+++ b/Version_Info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Obras\Documents\GitHub\Sistema-Financeiro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0521490-76C2-4408-AD5E-4AE386BF4557}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54662C21-E7E1-4E50-9CEC-BB33D90C330F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="13710" yWindow="2565" windowWidth="14685" windowHeight="12690" xr2:uid="{30F240C2-A098-48F6-BD2E-0F632F0648BA}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="105">
   <si>
     <t>major</t>
   </si>
@@ -383,6 +383,21 @@
   </si>
   <si>
     <t>Outras correções menores e melhorias de desempenho</t>
+  </si>
+  <si>
+    <t>Correção de edição no Visualizador de Lançamentos Fornecedor,</t>
+  </si>
+  <si>
+    <t>Correção de edição no Gerenciador de Lançamentos,</t>
+  </si>
+  <si>
+    <t>Melhoria na performance da AGENDA,</t>
+  </si>
+  <si>
+    <t>Inclusão de Referencia automática na AGENDA</t>
+  </si>
+  <si>
+    <t>Inclusão de botão INATIVAR/EXCLUIR fornecedores,</t>
   </si>
 </sst>
 </file>
@@ -813,7 +828,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8ECF308-2BDA-44B4-A992-93448DFE394D}">
-  <dimension ref="A1:E97"/>
+  <dimension ref="A1:E103"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="9.140625" style="2"/>
@@ -1521,8 +1536,50 @@
         <v>98</v>
       </c>
     </row>
-    <row r="97" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E97" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" s="2">
+        <v>1</v>
+      </c>
+      <c r="B98" s="2">
+        <v>6</v>
+      </c>
+      <c r="C98" s="2">
+        <v>0</v>
+      </c>
+      <c r="D98" s="3">
+        <v>46042</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E99" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E100" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E101" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E102" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E103" s="1" t="s">
         <v>99</v>
       </c>
     </row>

--- a/Version_Info.xlsx
+++ b/Version_Info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Obras\Documents\GitHub\Sistema-Financeiro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54662C21-E7E1-4E50-9CEC-BB33D90C330F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F76836FF-AC39-4444-AA4A-F1D2CE92A955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="13710" yWindow="2565" windowWidth="14685" windowHeight="12690" xr2:uid="{30F240C2-A098-48F6-BD2E-0F632F0648BA}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="107">
   <si>
     <t>major</t>
   </si>
@@ -398,6 +398,12 @@
   </si>
   <si>
     <t>Inclusão de botão INATIVAR/EXCLUIR fornecedores,</t>
+  </si>
+  <si>
+    <t>Inclusão de somatório no Gerenciador de Lançamentos</t>
+  </si>
+  <si>
+    <t>Melhoria nos filtros no Gerenciador de Lançamentos</t>
   </si>
 </sst>
 </file>
@@ -828,7 +834,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8ECF308-2BDA-44B4-A992-93448DFE394D}">
-  <dimension ref="A1:E103"/>
+  <dimension ref="A1:E105"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="9.140625" style="2"/>
@@ -1583,6 +1589,28 @@
         <v>99</v>
       </c>
     </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104" s="2">
+        <v>1</v>
+      </c>
+      <c r="B104" s="2">
+        <v>6</v>
+      </c>
+      <c r="C104" s="2">
+        <v>1</v>
+      </c>
+      <c r="D104" s="3">
+        <v>46058</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E105" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>

--- a/Version_Info.xlsx
+++ b/Version_Info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Obras\Documents\GitHub\Sistema-Financeiro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F76836FF-AC39-4444-AA4A-F1D2CE92A955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E41AC93-C531-4275-BDB9-A9D3BB74BB7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13710" yWindow="2565" windowWidth="14685" windowHeight="12690" xr2:uid="{30F240C2-A098-48F6-BD2E-0F632F0648BA}"/>
+    <workbookView xWindow="13755" yWindow="975" windowWidth="14685" windowHeight="12690" xr2:uid="{30F240C2-A098-48F6-BD2E-0F632F0648BA}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="112">
   <si>
     <t>major</t>
   </si>
@@ -404,6 +404,21 @@
   </si>
   <si>
     <t>Melhoria nos filtros no Gerenciador de Lançamentos</t>
+  </si>
+  <si>
+    <t>Reorganizada toda a lógica da Gestão de Empreiteiros</t>
+  </si>
+  <si>
+    <t>Redesenhado o Relatório Quinzenal de Medições para o modelo do cliente</t>
+  </si>
+  <si>
+    <t>Correção da aba Contratos da Gestão de Medições para carregar todos os contratos, independente do fornecedor</t>
+  </si>
+  <si>
+    <t>Inclusão de checkbox no Gerenciador de lançamentos para somar selecionados</t>
+  </si>
+  <si>
+    <t>Filtro de data do Gerenciador de Lançamentos traz a quinzena atual por padrão</t>
   </si>
 </sst>
 </file>
@@ -834,7 +849,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8ECF308-2BDA-44B4-A992-93448DFE394D}">
-  <dimension ref="A1:E105"/>
+  <dimension ref="A1:E110"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="9.140625" style="2"/>
@@ -1611,6 +1626,55 @@
         <v>106</v>
       </c>
     </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A106" s="2">
+        <v>1</v>
+      </c>
+      <c r="B106" s="2">
+        <v>7</v>
+      </c>
+      <c r="C106" s="2">
+        <v>0</v>
+      </c>
+      <c r="D106" s="3">
+        <v>46075</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E107" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108" s="2">
+        <v>1</v>
+      </c>
+      <c r="B108" s="2">
+        <v>7</v>
+      </c>
+      <c r="C108" s="2">
+        <v>1</v>
+      </c>
+      <c r="D108" s="3">
+        <v>46077</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E109" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E110" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>

--- a/Version_Info.xlsx
+++ b/Version_Info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Obras\Documents\GitHub\Sistema-Financeiro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E41AC93-C531-4275-BDB9-A9D3BB74BB7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BA7FDCA-9BEA-464A-B4C6-E915E83EF0A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13755" yWindow="975" windowWidth="14685" windowHeight="12690" xr2:uid="{30F240C2-A098-48F6-BD2E-0F632F0648BA}"/>
+    <workbookView xWindow="15465" yWindow="1245" windowWidth="13290" windowHeight="12690" xr2:uid="{30F240C2-A098-48F6-BD2E-0F632F0648BA}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="115">
   <si>
     <t>major</t>
   </si>
@@ -419,6 +419,15 @@
   </si>
   <si>
     <t>Filtro de data do Gerenciador de Lançamentos traz a quinzena atual por padrão</t>
+  </si>
+  <si>
+    <t>Inclusão do campo Responsável no formulário e na base de Fornecedores</t>
+  </si>
+  <si>
+    <t>Correção da busca por CNPJ/CPF do Visualizador de Lançamentos por Fornecedor</t>
+  </si>
+  <si>
+    <t>Atualização do Relatorio Quinzenal de Mediçoes - PDF para trazer o campo Responsável do Fornecedor</t>
   </si>
 </sst>
 </file>
@@ -849,7 +858,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8ECF308-2BDA-44B4-A992-93448DFE394D}">
-  <dimension ref="A1:E110"/>
+  <dimension ref="A1:E113"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="9.140625" style="2"/>
@@ -1675,6 +1684,33 @@
         <v>109</v>
       </c>
     </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A111" s="2">
+        <v>1</v>
+      </c>
+      <c r="B111" s="2">
+        <v>7</v>
+      </c>
+      <c r="C111" s="2">
+        <v>2</v>
+      </c>
+      <c r="D111" s="3">
+        <v>46084</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E112" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="113" spans="5:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E113" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>

--- a/Version_Info.xlsx
+++ b/Version_Info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Obras\Documents\GitHub\Sistema-Financeiro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BA7FDCA-9BEA-464A-B4C6-E915E83EF0A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{408641C1-0B8C-4E7E-ADD4-9367E45AE359}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15465" yWindow="1245" windowWidth="13290" windowHeight="12690" xr2:uid="{30F240C2-A098-48F6-BD2E-0F632F0648BA}"/>
+    <workbookView xWindow="15120" yWindow="900" windowWidth="13290" windowHeight="12690" xr2:uid="{30F240C2-A098-48F6-BD2E-0F632F0648BA}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="116">
   <si>
     <t>major</t>
   </si>
@@ -428,6 +428,9 @@
   </si>
   <si>
     <t>Atualização do Relatorio Quinzenal de Mediçoes - PDF para trazer o campo Responsável do Fornecedor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inclusão de aba SERVIÇOS ADICIONAIS ao exportar para o Excel o Relatório de Contratos de Medições </t>
   </si>
 </sst>
 </file>
@@ -858,7 +861,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8ECF308-2BDA-44B4-A992-93448DFE394D}">
-  <dimension ref="A1:E113"/>
+  <dimension ref="A1:E114"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="9.140625" style="2"/>
@@ -1708,6 +1711,11 @@
     </row>
     <row r="113" spans="5:5" ht="30" x14ac:dyDescent="0.25">
       <c r="E113" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="114" spans="5:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E114" s="1" t="s">
         <v>114</v>
       </c>
     </row>

--- a/Version_Info.xlsx
+++ b/Version_Info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Obras\Documents\GitHub\Sistema-Financeiro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{408641C1-0B8C-4E7E-ADD4-9367E45AE359}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37019DCE-E550-4C44-957C-A345C684F486}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15120" yWindow="900" windowWidth="13290" windowHeight="12690" xr2:uid="{30F240C2-A098-48F6-BD2E-0F632F0648BA}"/>
+    <workbookView xWindow="15210" yWindow="1080" windowWidth="13335" windowHeight="14430" xr2:uid="{30F240C2-A098-48F6-BD2E-0F632F0648BA}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="128">
   <si>
     <t>major</t>
   </si>
@@ -432,12 +432,87 @@
   <si>
     <t xml:space="preserve">Inclusão de aba SERVIÇOS ADICIONAIS ao exportar para o Excel o Relatório de Contratos de Medições </t>
   </si>
+  <si>
+    <t>Melhoria no Relatório de Medições, exportado do sistema, com índice e lista de fornecedores co Vínculo = EMPREITEIRO</t>
+  </si>
+  <si>
+    <t>Correção no relatório que compara a gestão de Medições e Taxa de Administração com registros em Dados</t>
+  </si>
+  <si>
+    <t>Inclusão de Importação de DIÁRIAS de Colaboradores</t>
+  </si>
+  <si>
+    <t>Correção de entrada automática do campo Status em Dados</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Inclusão de</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF032F62"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> relatório que compara a gestão de Medições e Taxa de Administração com registros em Dados</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inclusão de </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>vinculação de parcela de contrato de taxa de administração através do relatório acima</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inclusão de </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF24292E"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Relatório que mostra fornecedores individualmnete, por categoria, por cliente, etc.</t>
+    </r>
+  </si>
+  <si>
+    <t>Eliminação da necessidade de valor em contratos de administração de obras por percentual</t>
+  </si>
+  <si>
+    <t>Inclusão de gerador de contrato de administração de obras via Word</t>
+  </si>
+  <si>
+    <t>Inclusão do caminho Z:/servidor</t>
+  </si>
+  <si>
+    <t>Correção do módulo Gestão de Medições</t>
+  </si>
+  <si>
+    <t>Inclusão de Relatório Modelo para exportar para Excel quando não houver contrato de medição cadastrado</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -491,6 +566,24 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF24292E"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF032F62"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -512,7 +605,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -546,6 +639,9 @@
     </xf>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -861,7 +957,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8ECF308-2BDA-44B4-A992-93448DFE394D}">
-  <dimension ref="A1:E114"/>
+  <dimension ref="A1:E127"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="9.140625" style="2"/>
@@ -1709,14 +1805,110 @@
         <v>113</v>
       </c>
     </row>
-    <row r="113" spans="5:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="E113" s="1" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="114" spans="5:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="E114" s="1" t="s">
         <v>114</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A115" s="2">
+        <v>1</v>
+      </c>
+      <c r="B115" s="2">
+        <v>7</v>
+      </c>
+      <c r="C115" s="2">
+        <v>3</v>
+      </c>
+      <c r="D115" s="3">
+        <v>46120</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E116" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E117" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E118" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A120" s="2">
+        <v>1</v>
+      </c>
+      <c r="B120" s="2">
+        <v>7</v>
+      </c>
+      <c r="C120" s="2">
+        <v>4</v>
+      </c>
+      <c r="D120" s="3">
+        <v>46164</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E121" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E122" s="12" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E123" s="12" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A124" s="2">
+        <v>1</v>
+      </c>
+      <c r="B124" s="2">
+        <v>7</v>
+      </c>
+      <c r="C124" s="2">
+        <v>5</v>
+      </c>
+      <c r="D124" s="3">
+        <v>46183</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E125" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="E126" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E127" s="1" t="s">
+        <v>118</v>
       </c>
     </row>
   </sheetData>
